--- a/Rincian Penjualan-2026-05-01__2026-05-01.xlsx
+++ b/Rincian Penjualan-2026-05-01__2026-05-01.xlsx
@@ -1137,7 +1137,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="12" max="12" width="9" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.2" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
     <col min="16" max="16" width="0.1" customWidth="1"/>
     <col min="17" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
